--- a/CAISSE_PARADISE_ALUMINIUM_10-2026.xlsx
+++ b/CAISSE_PARADISE_ALUMINIUM_10-2026.xlsx
@@ -112,244 +112,244 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="001B2430"/>
+      <color rgb="FF1B2430"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="005B6675"/>
+      <color rgb="FF5B6675"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="15"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C8A24B"/>
+      <color rgb="FFC8A24B"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00021F47"/>
+      <color rgb="FF021F47"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00021F47"/>
+      <color rgb="FF021F47"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="001A56A0"/>
+      <color rgb="FF1A56A0"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="001B2430"/>
+      <color rgb="FF1B2430"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001B2430"/>
+      <color rgb="FF1B2430"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001B2430"/>
+      <color rgb="FF1B2430"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00A8231C"/>
+      <color rgb="FFA8231C"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00A8231C"/>
+      <color rgb="FFA8231C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="001A56A0"/>
+      <color rgb="FF1A56A0"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="001B2430"/>
+      <color rgb="FF1B2430"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00A8231C"/>
+      <color rgb="FFA8231C"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001E6B3A"/>
+      <color rgb="FF1E6B3A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00021F47"/>
+      <color rgb="FF021F47"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="005B6675"/>
+      <color rgb="FF5B6675"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C8A24B"/>
+      <color rgb="FFC8A24B"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00021F47"/>
+      <color rgb="FF021F47"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00A8231C"/>
+      <color rgb="FFA8231C"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="008A5A00"/>
+      <color rgb="FF8A5A00"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001E6B3A"/>
+      <color rgb="FF1E6B3A"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00021F47"/>
+      <color rgb="FF021F47"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="001E6B3A"/>
+      <color rgb="FF1E6B3A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00021F47"/>
+      <color rgb="FF021F47"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00021F47"/>
+      <color rgb="FF021F47"/>
       <sz val="17"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="005B6675"/>
+      <color rgb="FF5B6675"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001E6B3A"/>
+      <color rgb="FF1E6B3A"/>
       <sz val="17"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="003B5C8F"/>
+      <color rgb="FF3B5C8F"/>
       <sz val="17"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00A8231C"/>
+      <color rgb="FFA8231C"/>
       <sz val="17"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="008A5A00"/>
+      <color rgb="FF8A5A00"/>
       <sz val="17"/>
     </font>
   </fonts>
@@ -362,62 +362,62 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003B5C8F"/>
+        <fgColor rgb="FF3B5C8F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00021F47"/>
+        <fgColor rgb="FF021F47"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3D6"/>
+        <fgColor rgb="FFFFF3D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EDF5"/>
+        <fgColor rgb="FFE8EDF5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF7D6"/>
+        <fgColor rgb="FFFFF7D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000B2E5E"/>
+        <fgColor rgb="FF0B2E5E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F5F9"/>
+        <fgColor rgb="FFF3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005B6675"/>
+        <fgColor rgb="FF5B6675"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E6B3A"/>
+        <fgColor rgb="FF1E6B3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A8231C"/>
+        <fgColor rgb="FFA8231C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008A5A00"/>
+        <fgColor rgb="FF8A5A00"/>
       </patternFill>
     </fill>
   </fills>
@@ -431,56 +431,56 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="003B5C8F"/>
+        <color rgb="FF3B5C8F"/>
       </left>
       <right style="thin">
-        <color rgb="003B5C8F"/>
+        <color rgb="FF3B5C8F"/>
       </right>
       <top style="thin">
-        <color rgb="003B5C8F"/>
+        <color rgb="FF3B5C8F"/>
       </top>
       <bottom style="thin">
-        <color rgb="003B5C8F"/>
+        <color rgb="FF3B5C8F"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="00E8EDF5"/>
+        <color rgb="FFE8EDF5"/>
       </top>
       <bottom style="medium">
-        <color rgb="00C8A24B"/>
+        <color rgb="FFC8A24B"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00DDE2EA"/>
+        <color rgb="FFDDE2EA"/>
       </left>
       <right style="thin">
-        <color rgb="00DDE2EA"/>
+        <color rgb="FFDDE2EA"/>
       </right>
       <top style="thin">
-        <color rgb="00DDE2EA"/>
+        <color rgb="FFDDE2EA"/>
       </top>
       <bottom style="thin">
-        <color rgb="00DDE2EA"/>
+        <color rgb="FFDDE2EA"/>
       </bottom>
     </border>
     <border>
       <top style="medium">
-        <color rgb="00C8A24B"/>
+        <color rgb="FFC8A24B"/>
       </top>
     </border>
     <border>
       <left/>
       <right/>
       <top style="medium">
-        <color rgb="00C8A24B"/>
+        <color rgb="FFC8A24B"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -489,7 +489,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00E8EDF5"/>
+        <color rgb="FFE8EDF5"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -497,10 +497,10 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="00E8EDF5"/>
+        <color rgb="FFE8EDF5"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -508,13 +508,13 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="00E8EDF5"/>
+        <color rgb="FFE8EDF5"/>
       </top>
       <bottom style="medium">
-        <color rgb="00C8A24B"/>
+        <color rgb="FFC8A24B"/>
       </bottom>
       <diagonal/>
     </border>
@@ -785,7 +785,7 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00A8231C"/>
+        <color rgb="FFA8231C"/>
         <sz val="17"/>
       </font>
     </dxf>
@@ -793,12 +793,12 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00A8231C"/>
+        <color rgb="FFA8231C"/>
         <sz val="10"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FBE7E5"/>
+        <patternFill>
+          <bgColor rgb="FFFBE7E5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -806,7 +806,7 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="001E6B3A"/>
+        <color rgb="FF1E6B3A"/>
         <sz val="10"/>
       </font>
     </dxf>
@@ -814,26 +814,26 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
         <sz val="10"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00A8231C"/>
+        <patternFill>
+          <bgColor rgb="FFA8231C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FBE7E5"/>
+        <patternFill>
+          <bgColor rgb="FFFBE7E5"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00A8231C"/>
+        <patternFill>
+          <bgColor rgb="FFA8231C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -841,7 +841,7 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00021F47"/>
+        <color rgb="FF021F47"/>
         <sz val="10"/>
       </font>
     </dxf>
@@ -849,12 +849,12 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00A8231C"/>
+        <color rgb="FFA8231C"/>
         <sz val="9.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FBE7E5"/>
+        <patternFill>
+          <bgColor rgb="FFFBE7E5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -862,12 +862,12 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="008A5A00"/>
+        <color rgb="FF8A5A00"/>
         <sz val="9.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFF3D6"/>
+        <patternFill>
+          <bgColor rgb="FFFFF3D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -875,12 +875,12 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="001E6B3A"/>
+        <color rgb="FF1E6B3A"/>
         <sz val="9.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00E4F1E8"/>
+        <patternFill>
+          <bgColor rgb="FFE4F1E8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -888,12 +888,12 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="005B6675"/>
+        <color rgb="FF5B6675"/>
         <sz val="9.5"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00E8EDF5"/>
+        <patternFill>
+          <bgColor rgb="FFE8EDF5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1439,471 +1439,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment11.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment12.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment14.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment15.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment16.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment17.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment18.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment19.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment20.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment21.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment22.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment23.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment24.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment25.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment26.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment27.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment28.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment29.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment30.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment31.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Paradise Aluminium</author>
-  </authors>
-  <commentList>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Comptez les espèces dans la caisse PARADISE le soir et notez le montant ici. L'écart se calcule tout seul.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -4063,7 +3598,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -5467,7 +5001,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -6871,7 +6404,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -8275,7 +7807,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -9679,7 +9210,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -11083,7 +10613,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -12487,7 +12016,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -13891,7 +13419,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -15295,7 +14822,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -16699,7 +16225,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -21074,7 +20599,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -22478,7 +22002,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -23882,7 +23405,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -25286,7 +24808,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -26690,7 +26211,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -28094,7 +27614,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -29498,7 +29017,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -30902,7 +30420,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -32306,7 +31823,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -33710,7 +33226,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -35114,7 +34629,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -36518,7 +36032,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -37922,7 +37435,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -39326,7 +38838,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -40730,7 +40241,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -41897,7 +41407,7 @@
       </c>
       <c r="E5" s="26" t="n"/>
       <c r="F5" s="83">
-        <f>SUMIF($H$9:$H$148,"À ÉCHOIR ≤ 30 J",$F$9:$F$148)</f>
+        <f>SUMIF($H$9:$H$148,"À ÉCHOIR SOUS 30 J",$F$9:$F$148)</f>
         <v/>
       </c>
       <c r="G5" s="26" t="n"/>
@@ -41970,7 +41480,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="87">
-        <f>IF(AND($B9="",$D9=""),"",IF($F9&lt;=0,"PAYÉ",IF($B9="","SANS DATE",IF($B9&lt;TODAY(),"EN RETARD",IF($B9&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B9="",$D9=""),"",IF($F9&lt;=0,"PAYÉ",IF($B9="","SANS DATE",IF($B9&lt;TODAY(),"EN RETARD",IF($B9&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I9" s="51" t="inlineStr"/>
@@ -41993,7 +41503,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="87">
-        <f>IF(AND($B10="",$D10=""),"",IF($F10&lt;=0,"PAYÉ",IF($B10="","SANS DATE",IF($B10&lt;TODAY(),"EN RETARD",IF($B10&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B10="",$D10=""),"",IF($F10&lt;=0,"PAYÉ",IF($B10="","SANS DATE",IF($B10&lt;TODAY(),"EN RETARD",IF($B10&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I10" s="51" t="inlineStr"/>
@@ -42016,7 +41526,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="87">
-        <f>IF(AND($B11="",$D11=""),"",IF($F11&lt;=0,"PAYÉ",IF($B11="","SANS DATE",IF($B11&lt;TODAY(),"EN RETARD",IF($B11&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B11="",$D11=""),"",IF($F11&lt;=0,"PAYÉ",IF($B11="","SANS DATE",IF($B11&lt;TODAY(),"EN RETARD",IF($B11&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I11" s="51" t="inlineStr"/>
@@ -42039,7 +41549,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="87">
-        <f>IF(AND($B12="",$D12=""),"",IF($F12&lt;=0,"PAYÉ",IF($B12="","SANS DATE",IF($B12&lt;TODAY(),"EN RETARD",IF($B12&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B12="",$D12=""),"",IF($F12&lt;=0,"PAYÉ",IF($B12="","SANS DATE",IF($B12&lt;TODAY(),"EN RETARD",IF($B12&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I12" s="51" t="inlineStr">
@@ -42066,7 +41576,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="87">
-        <f>IF(AND($B13="",$D13=""),"",IF($F13&lt;=0,"PAYÉ",IF($B13="","SANS DATE",IF($B13&lt;TODAY(),"EN RETARD",IF($B13&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B13="",$D13=""),"",IF($F13&lt;=0,"PAYÉ",IF($B13="","SANS DATE",IF($B13&lt;TODAY(),"EN RETARD",IF($B13&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I13" s="51" t="inlineStr">
@@ -42093,7 +41603,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="87">
-        <f>IF(AND($B14="",$D14=""),"",IF($F14&lt;=0,"PAYÉ",IF($B14="","SANS DATE",IF($B14&lt;TODAY(),"EN RETARD",IF($B14&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B14="",$D14=""),"",IF($F14&lt;=0,"PAYÉ",IF($B14="","SANS DATE",IF($B14&lt;TODAY(),"EN RETARD",IF($B14&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I14" s="51" t="inlineStr">
@@ -42124,7 +41634,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="87">
-        <f>IF(AND($B15="",$D15=""),"",IF($F15&lt;=0,"PAYÉ",IF($B15="","SANS DATE",IF($B15&lt;TODAY(),"EN RETARD",IF($B15&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B15="",$D15=""),"",IF($F15&lt;=0,"PAYÉ",IF($B15="","SANS DATE",IF($B15&lt;TODAY(),"EN RETARD",IF($B15&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I15" s="51" t="inlineStr"/>
@@ -42147,7 +41657,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="87">
-        <f>IF(AND($B16="",$D16=""),"",IF($F16&lt;=0,"PAYÉ",IF($B16="","SANS DATE",IF($B16&lt;TODAY(),"EN RETARD",IF($B16&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B16="",$D16=""),"",IF($F16&lt;=0,"PAYÉ",IF($B16="","SANS DATE",IF($B16&lt;TODAY(),"EN RETARD",IF($B16&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I16" s="51" t="inlineStr"/>
@@ -42170,7 +41680,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="87">
-        <f>IF(AND($B17="",$D17=""),"",IF($F17&lt;=0,"PAYÉ",IF($B17="","SANS DATE",IF($B17&lt;TODAY(),"EN RETARD",IF($B17&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B17="",$D17=""),"",IF($F17&lt;=0,"PAYÉ",IF($B17="","SANS DATE",IF($B17&lt;TODAY(),"EN RETARD",IF($B17&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I17" s="51" t="inlineStr"/>
@@ -42201,7 +41711,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="87">
-        <f>IF(AND($B18="",$D18=""),"",IF($F18&lt;=0,"PAYÉ",IF($B18="","SANS DATE",IF($B18&lt;TODAY(),"EN RETARD",IF($B18&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B18="",$D18=""),"",IF($F18&lt;=0,"PAYÉ",IF($B18="","SANS DATE",IF($B18&lt;TODAY(),"EN RETARD",IF($B18&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I18" s="51" t="inlineStr">
@@ -42236,7 +41746,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="87">
-        <f>IF(AND($B19="",$D19=""),"",IF($F19&lt;=0,"PAYÉ",IF($B19="","SANS DATE",IF($B19&lt;TODAY(),"EN RETARD",IF($B19&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B19="",$D19=""),"",IF($F19&lt;=0,"PAYÉ",IF($B19="","SANS DATE",IF($B19&lt;TODAY(),"EN RETARD",IF($B19&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I19" s="51" t="inlineStr">
@@ -42271,7 +41781,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="87">
-        <f>IF(AND($B20="",$D20=""),"",IF($F20&lt;=0,"PAYÉ",IF($B20="","SANS DATE",IF($B20&lt;TODAY(),"EN RETARD",IF($B20&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B20="",$D20=""),"",IF($F20&lt;=0,"PAYÉ",IF($B20="","SANS DATE",IF($B20&lt;TODAY(),"EN RETARD",IF($B20&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I20" s="51" t="inlineStr">
@@ -42302,7 +41812,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="87">
-        <f>IF(AND($B21="",$D21=""),"",IF($F21&lt;=0,"PAYÉ",IF($B21="","SANS DATE",IF($B21&lt;TODAY(),"EN RETARD",IF($B21&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B21="",$D21=""),"",IF($F21&lt;=0,"PAYÉ",IF($B21="","SANS DATE",IF($B21&lt;TODAY(),"EN RETARD",IF($B21&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I21" s="51" t="inlineStr"/>
@@ -42331,7 +41841,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="87">
-        <f>IF(AND($B22="",$D22=""),"",IF($F22&lt;=0,"PAYÉ",IF($B22="","SANS DATE",IF($B22&lt;TODAY(),"EN RETARD",IF($B22&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B22="",$D22=""),"",IF($F22&lt;=0,"PAYÉ",IF($B22="","SANS DATE",IF($B22&lt;TODAY(),"EN RETARD",IF($B22&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I22" s="51" t="inlineStr"/>
@@ -42358,7 +41868,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="87">
-        <f>IF(AND($B23="",$D23=""),"",IF($F23&lt;=0,"PAYÉ",IF($B23="","SANS DATE",IF($B23&lt;TODAY(),"EN RETARD",IF($B23&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B23="",$D23=""),"",IF($F23&lt;=0,"PAYÉ",IF($B23="","SANS DATE",IF($B23&lt;TODAY(),"EN RETARD",IF($B23&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I23" s="51" t="inlineStr"/>
@@ -42385,7 +41895,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="87">
-        <f>IF(AND($B24="",$D24=""),"",IF($F24&lt;=0,"PAYÉ",IF($B24="","SANS DATE",IF($B24&lt;TODAY(),"EN RETARD",IF($B24&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B24="",$D24=""),"",IF($F24&lt;=0,"PAYÉ",IF($B24="","SANS DATE",IF($B24&lt;TODAY(),"EN RETARD",IF($B24&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I24" s="51" t="inlineStr"/>
@@ -42412,7 +41922,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="87">
-        <f>IF(AND($B25="",$D25=""),"",IF($F25&lt;=0,"PAYÉ",IF($B25="","SANS DATE",IF($B25&lt;TODAY(),"EN RETARD",IF($B25&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B25="",$D25=""),"",IF($F25&lt;=0,"PAYÉ",IF($B25="","SANS DATE",IF($B25&lt;TODAY(),"EN RETARD",IF($B25&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I25" s="51" t="inlineStr"/>
@@ -42439,7 +41949,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="87">
-        <f>IF(AND($B26="",$D26=""),"",IF($F26&lt;=0,"PAYÉ",IF($B26="","SANS DATE",IF($B26&lt;TODAY(),"EN RETARD",IF($B26&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B26="",$D26=""),"",IF($F26&lt;=0,"PAYÉ",IF($B26="","SANS DATE",IF($B26&lt;TODAY(),"EN RETARD",IF($B26&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I26" s="51" t="inlineStr"/>
@@ -42466,7 +41976,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="87">
-        <f>IF(AND($B27="",$D27=""),"",IF($F27&lt;=0,"PAYÉ",IF($B27="","SANS DATE",IF($B27&lt;TODAY(),"EN RETARD",IF($B27&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B27="",$D27=""),"",IF($F27&lt;=0,"PAYÉ",IF($B27="","SANS DATE",IF($B27&lt;TODAY(),"EN RETARD",IF($B27&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I27" s="51" t="inlineStr"/>
@@ -42493,7 +42003,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="87">
-        <f>IF(AND($B28="",$D28=""),"",IF($F28&lt;=0,"PAYÉ",IF($B28="","SANS DATE",IF($B28&lt;TODAY(),"EN RETARD",IF($B28&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B28="",$D28=""),"",IF($F28&lt;=0,"PAYÉ",IF($B28="","SANS DATE",IF($B28&lt;TODAY(),"EN RETARD",IF($B28&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I28" s="51" t="inlineStr"/>
@@ -42520,7 +42030,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="87">
-        <f>IF(AND($B29="",$D29=""),"",IF($F29&lt;=0,"PAYÉ",IF($B29="","SANS DATE",IF($B29&lt;TODAY(),"EN RETARD",IF($B29&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B29="",$D29=""),"",IF($F29&lt;=0,"PAYÉ",IF($B29="","SANS DATE",IF($B29&lt;TODAY(),"EN RETARD",IF($B29&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I29" s="51" t="inlineStr"/>
@@ -42547,7 +42057,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="87">
-        <f>IF(AND($B30="",$D30=""),"",IF($F30&lt;=0,"PAYÉ",IF($B30="","SANS DATE",IF($B30&lt;TODAY(),"EN RETARD",IF($B30&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B30="",$D30=""),"",IF($F30&lt;=0,"PAYÉ",IF($B30="","SANS DATE",IF($B30&lt;TODAY(),"EN RETARD",IF($B30&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I30" s="51" t="inlineStr"/>
@@ -42574,7 +42084,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="87">
-        <f>IF(AND($B31="",$D31=""),"",IF($F31&lt;=0,"PAYÉ",IF($B31="","SANS DATE",IF($B31&lt;TODAY(),"EN RETARD",IF($B31&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B31="",$D31=""),"",IF($F31&lt;=0,"PAYÉ",IF($B31="","SANS DATE",IF($B31&lt;TODAY(),"EN RETARD",IF($B31&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I31" s="51" t="inlineStr"/>
@@ -42601,7 +42111,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="87">
-        <f>IF(AND($B32="",$D32=""),"",IF($F32&lt;=0,"PAYÉ",IF($B32="","SANS DATE",IF($B32&lt;TODAY(),"EN RETARD",IF($B32&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B32="",$D32=""),"",IF($F32&lt;=0,"PAYÉ",IF($B32="","SANS DATE",IF($B32&lt;TODAY(),"EN RETARD",IF($B32&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I32" s="51" t="inlineStr"/>
@@ -42628,7 +42138,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="87">
-        <f>IF(AND($B33="",$D33=""),"",IF($F33&lt;=0,"PAYÉ",IF($B33="","SANS DATE",IF($B33&lt;TODAY(),"EN RETARD",IF($B33&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B33="",$D33=""),"",IF($F33&lt;=0,"PAYÉ",IF($B33="","SANS DATE",IF($B33&lt;TODAY(),"EN RETARD",IF($B33&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I33" s="51" t="inlineStr"/>
@@ -42655,7 +42165,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="87">
-        <f>IF(AND($B34="",$D34=""),"",IF($F34&lt;=0,"PAYÉ",IF($B34="","SANS DATE",IF($B34&lt;TODAY(),"EN RETARD",IF($B34&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B34="",$D34=""),"",IF($F34&lt;=0,"PAYÉ",IF($B34="","SANS DATE",IF($B34&lt;TODAY(),"EN RETARD",IF($B34&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I34" s="51" t="inlineStr"/>
@@ -42682,7 +42192,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="87">
-        <f>IF(AND($B35="",$D35=""),"",IF($F35&lt;=0,"PAYÉ",IF($B35="","SANS DATE",IF($B35&lt;TODAY(),"EN RETARD",IF($B35&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B35="",$D35=""),"",IF($F35&lt;=0,"PAYÉ",IF($B35="","SANS DATE",IF($B35&lt;TODAY(),"EN RETARD",IF($B35&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I35" s="51" t="inlineStr"/>
@@ -42709,7 +42219,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="87">
-        <f>IF(AND($B36="",$D36=""),"",IF($F36&lt;=0,"PAYÉ",IF($B36="","SANS DATE",IF($B36&lt;TODAY(),"EN RETARD",IF($B36&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B36="",$D36=""),"",IF($F36&lt;=0,"PAYÉ",IF($B36="","SANS DATE",IF($B36&lt;TODAY(),"EN RETARD",IF($B36&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I36" s="51" t="inlineStr"/>
@@ -42736,7 +42246,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="87">
-        <f>IF(AND($B37="",$D37=""),"",IF($F37&lt;=0,"PAYÉ",IF($B37="","SANS DATE",IF($B37&lt;TODAY(),"EN RETARD",IF($B37&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B37="",$D37=""),"",IF($F37&lt;=0,"PAYÉ",IF($B37="","SANS DATE",IF($B37&lt;TODAY(),"EN RETARD",IF($B37&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I37" s="51" t="inlineStr"/>
@@ -42763,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="87">
-        <f>IF(AND($B38="",$D38=""),"",IF($F38&lt;=0,"PAYÉ",IF($B38="","SANS DATE",IF($B38&lt;TODAY(),"EN RETARD",IF($B38&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B38="",$D38=""),"",IF($F38&lt;=0,"PAYÉ",IF($B38="","SANS DATE",IF($B38&lt;TODAY(),"EN RETARD",IF($B38&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I38" s="51" t="inlineStr"/>
@@ -42790,7 +42300,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="87">
-        <f>IF(AND($B39="",$D39=""),"",IF($F39&lt;=0,"PAYÉ",IF($B39="","SANS DATE",IF($B39&lt;TODAY(),"EN RETARD",IF($B39&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B39="",$D39=""),"",IF($F39&lt;=0,"PAYÉ",IF($B39="","SANS DATE",IF($B39&lt;TODAY(),"EN RETARD",IF($B39&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I39" s="51" t="inlineStr"/>
@@ -42817,7 +42327,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="87">
-        <f>IF(AND($B40="",$D40=""),"",IF($F40&lt;=0,"PAYÉ",IF($B40="","SANS DATE",IF($B40&lt;TODAY(),"EN RETARD",IF($B40&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B40="",$D40=""),"",IF($F40&lt;=0,"PAYÉ",IF($B40="","SANS DATE",IF($B40&lt;TODAY(),"EN RETARD",IF($B40&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I40" s="51" t="inlineStr"/>
@@ -42844,7 +42354,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="87">
-        <f>IF(AND($B41="",$D41=""),"",IF($F41&lt;=0,"PAYÉ",IF($B41="","SANS DATE",IF($B41&lt;TODAY(),"EN RETARD",IF($B41&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B41="",$D41=""),"",IF($F41&lt;=0,"PAYÉ",IF($B41="","SANS DATE",IF($B41&lt;TODAY(),"EN RETARD",IF($B41&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I41" s="51" t="inlineStr"/>
@@ -42875,7 +42385,7 @@
         <v>30000</v>
       </c>
       <c r="H42" s="87">
-        <f>IF(AND($B42="",$D42=""),"",IF($F42&lt;=0,"PAYÉ",IF($B42="","SANS DATE",IF($B42&lt;TODAY(),"EN RETARD",IF($B42&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B42="",$D42=""),"",IF($F42&lt;=0,"PAYÉ",IF($B42="","SANS DATE",IF($B42&lt;TODAY(),"EN RETARD",IF($B42&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I42" s="51" t="inlineStr"/>
@@ -42902,7 +42412,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="87">
-        <f>IF(AND($B43="",$D43=""),"",IF($F43&lt;=0,"PAYÉ",IF($B43="","SANS DATE",IF($B43&lt;TODAY(),"EN RETARD",IF($B43&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B43="",$D43=""),"",IF($F43&lt;=0,"PAYÉ",IF($B43="","SANS DATE",IF($B43&lt;TODAY(),"EN RETARD",IF($B43&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I43" s="51" t="inlineStr"/>
@@ -42933,7 +42443,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="87">
-        <f>IF(AND($B44="",$D44=""),"",IF($F44&lt;=0,"PAYÉ",IF($B44="","SANS DATE",IF($B44&lt;TODAY(),"EN RETARD",IF($B44&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B44="",$D44=""),"",IF($F44&lt;=0,"PAYÉ",IF($B44="","SANS DATE",IF($B44&lt;TODAY(),"EN RETARD",IF($B44&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I44" s="51" t="inlineStr"/>
@@ -42964,7 +42474,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="87">
-        <f>IF(AND($B45="",$D45=""),"",IF($F45&lt;=0,"PAYÉ",IF($B45="","SANS DATE",IF($B45&lt;TODAY(),"EN RETARD",IF($B45&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B45="",$D45=""),"",IF($F45&lt;=0,"PAYÉ",IF($B45="","SANS DATE",IF($B45&lt;TODAY(),"EN RETARD",IF($B45&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I45" s="51" t="inlineStr"/>
@@ -42995,7 +42505,7 @@
         <v>29000</v>
       </c>
       <c r="H46" s="87">
-        <f>IF(AND($B46="",$D46=""),"",IF($F46&lt;=0,"PAYÉ",IF($B46="","SANS DATE",IF($B46&lt;TODAY(),"EN RETARD",IF($B46&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B46="",$D46=""),"",IF($F46&lt;=0,"PAYÉ",IF($B46="","SANS DATE",IF($B46&lt;TODAY(),"EN RETARD",IF($B46&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I46" s="51" t="inlineStr">
@@ -43030,7 +42540,7 @@
         <v>25400</v>
       </c>
       <c r="H47" s="87">
-        <f>IF(AND($B47="",$D47=""),"",IF($F47&lt;=0,"PAYÉ",IF($B47="","SANS DATE",IF($B47&lt;TODAY(),"EN RETARD",IF($B47&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B47="",$D47=""),"",IF($F47&lt;=0,"PAYÉ",IF($B47="","SANS DATE",IF($B47&lt;TODAY(),"EN RETARD",IF($B47&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I47" s="51" t="inlineStr">
@@ -43065,7 +42575,7 @@
         <v>19460.1</v>
       </c>
       <c r="H48" s="87">
-        <f>IF(AND($B48="",$D48=""),"",IF($F48&lt;=0,"PAYÉ",IF($B48="","SANS DATE",IF($B48&lt;TODAY(),"EN RETARD",IF($B48&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B48="",$D48=""),"",IF($F48&lt;=0,"PAYÉ",IF($B48="","SANS DATE",IF($B48&lt;TODAY(),"EN RETARD",IF($B48&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I48" s="51" t="inlineStr">
@@ -43100,7 +42610,7 @@
         <v>4610</v>
       </c>
       <c r="H49" s="87">
-        <f>IF(AND($B49="",$D49=""),"",IF($F49&lt;=0,"PAYÉ",IF($B49="","SANS DATE",IF($B49&lt;TODAY(),"EN RETARD",IF($B49&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B49="",$D49=""),"",IF($F49&lt;=0,"PAYÉ",IF($B49="","SANS DATE",IF($B49&lt;TODAY(),"EN RETARD",IF($B49&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I49" s="51" t="inlineStr">
@@ -43135,7 +42645,7 @@
         <v>17572</v>
       </c>
       <c r="H50" s="87">
-        <f>IF(AND($B50="",$D50=""),"",IF($F50&lt;=0,"PAYÉ",IF($B50="","SANS DATE",IF($B50&lt;TODAY(),"EN RETARD",IF($B50&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B50="",$D50=""),"",IF($F50&lt;=0,"PAYÉ",IF($B50="","SANS DATE",IF($B50&lt;TODAY(),"EN RETARD",IF($B50&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I50" s="51" t="inlineStr">
@@ -43170,7 +42680,7 @@
         <v>29000</v>
       </c>
       <c r="H51" s="87">
-        <f>IF(AND($B51="",$D51=""),"",IF($F51&lt;=0,"PAYÉ",IF($B51="","SANS DATE",IF($B51&lt;TODAY(),"EN RETARD",IF($B51&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B51="",$D51=""),"",IF($F51&lt;=0,"PAYÉ",IF($B51="","SANS DATE",IF($B51&lt;TODAY(),"EN RETARD",IF($B51&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I51" s="51" t="inlineStr">
@@ -43201,7 +42711,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="87">
-        <f>IF(AND($B52="",$D52=""),"",IF($F52&lt;=0,"PAYÉ",IF($B52="","SANS DATE",IF($B52&lt;TODAY(),"EN RETARD",IF($B52&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B52="",$D52=""),"",IF($F52&lt;=0,"PAYÉ",IF($B52="","SANS DATE",IF($B52&lt;TODAY(),"EN RETARD",IF($B52&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I52" s="51" t="inlineStr"/>
@@ -43228,7 +42738,7 @@
         <v>8000</v>
       </c>
       <c r="H53" s="87">
-        <f>IF(AND($B53="",$D53=""),"",IF($F53&lt;=0,"PAYÉ",IF($B53="","SANS DATE",IF($B53&lt;TODAY(),"EN RETARD",IF($B53&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B53="",$D53=""),"",IF($F53&lt;=0,"PAYÉ",IF($B53="","SANS DATE",IF($B53&lt;TODAY(),"EN RETARD",IF($B53&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I53" s="51" t="inlineStr">
@@ -43259,7 +42769,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="87">
-        <f>IF(AND($B54="",$D54=""),"",IF($F54&lt;=0,"PAYÉ",IF($B54="","SANS DATE",IF($B54&lt;TODAY(),"EN RETARD",IF($B54&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B54="",$D54=""),"",IF($F54&lt;=0,"PAYÉ",IF($B54="","SANS DATE",IF($B54&lt;TODAY(),"EN RETARD",IF($B54&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I54" s="51" t="inlineStr"/>
@@ -43286,7 +42796,7 @@
         <v>4503.03</v>
       </c>
       <c r="H55" s="87">
-        <f>IF(AND($B55="",$D55=""),"",IF($F55&lt;=0,"PAYÉ",IF($B55="","SANS DATE",IF($B55&lt;TODAY(),"EN RETARD",IF($B55&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B55="",$D55=""),"",IF($F55&lt;=0,"PAYÉ",IF($B55="","SANS DATE",IF($B55&lt;TODAY(),"EN RETARD",IF($B55&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I55" s="51" t="inlineStr">
@@ -43321,7 +42831,7 @@
         <v>15000</v>
       </c>
       <c r="H56" s="87">
-        <f>IF(AND($B56="",$D56=""),"",IF($F56&lt;=0,"PAYÉ",IF($B56="","SANS DATE",IF($B56&lt;TODAY(),"EN RETARD",IF($B56&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B56="",$D56=""),"",IF($F56&lt;=0,"PAYÉ",IF($B56="","SANS DATE",IF($B56&lt;TODAY(),"EN RETARD",IF($B56&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I56" s="51" t="inlineStr">
@@ -43356,7 +42866,7 @@
         <v>16372</v>
       </c>
       <c r="H57" s="87">
-        <f>IF(AND($B57="",$D57=""),"",IF($F57&lt;=0,"PAYÉ",IF($B57="","SANS DATE",IF($B57&lt;TODAY(),"EN RETARD",IF($B57&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B57="",$D57=""),"",IF($F57&lt;=0,"PAYÉ",IF($B57="","SANS DATE",IF($B57&lt;TODAY(),"EN RETARD",IF($B57&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I57" s="51" t="inlineStr">
@@ -43391,7 +42901,7 @@
         <v>30400</v>
       </c>
       <c r="H58" s="87">
-        <f>IF(AND($B58="",$D58=""),"",IF($F58&lt;=0,"PAYÉ",IF($B58="","SANS DATE",IF($B58&lt;TODAY(),"EN RETARD",IF($B58&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B58="",$D58=""),"",IF($F58&lt;=0,"PAYÉ",IF($B58="","SANS DATE",IF($B58&lt;TODAY(),"EN RETARD",IF($B58&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I58" s="51" t="inlineStr">
@@ -43426,7 +42936,7 @@
         <v>22155</v>
       </c>
       <c r="H59" s="87">
-        <f>IF(AND($B59="",$D59=""),"",IF($F59&lt;=0,"PAYÉ",IF($B59="","SANS DATE",IF($B59&lt;TODAY(),"EN RETARD",IF($B59&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B59="",$D59=""),"",IF($F59&lt;=0,"PAYÉ",IF($B59="","SANS DATE",IF($B59&lt;TODAY(),"EN RETARD",IF($B59&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I59" s="51" t="inlineStr">
@@ -43461,7 +42971,7 @@
         <v>28000</v>
       </c>
       <c r="H60" s="87">
-        <f>IF(AND($B60="",$D60=""),"",IF($F60&lt;=0,"PAYÉ",IF($B60="","SANS DATE",IF($B60&lt;TODAY(),"EN RETARD",IF($B60&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B60="",$D60=""),"",IF($F60&lt;=0,"PAYÉ",IF($B60="","SANS DATE",IF($B60&lt;TODAY(),"EN RETARD",IF($B60&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I60" s="51" t="inlineStr">
@@ -43496,7 +43006,7 @@
         <v>933</v>
       </c>
       <c r="H61" s="87">
-        <f>IF(AND($B61="",$D61=""),"",IF($F61&lt;=0,"PAYÉ",IF($B61="","SANS DATE",IF($B61&lt;TODAY(),"EN RETARD",IF($B61&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B61="",$D61=""),"",IF($F61&lt;=0,"PAYÉ",IF($B61="","SANS DATE",IF($B61&lt;TODAY(),"EN RETARD",IF($B61&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I61" s="51" t="inlineStr">
@@ -43531,7 +43041,7 @@
         <v>17500</v>
       </c>
       <c r="H62" s="87">
-        <f>IF(AND($B62="",$D62=""),"",IF($F62&lt;=0,"PAYÉ",IF($B62="","SANS DATE",IF($B62&lt;TODAY(),"EN RETARD",IF($B62&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B62="",$D62=""),"",IF($F62&lt;=0,"PAYÉ",IF($B62="","SANS DATE",IF($B62&lt;TODAY(),"EN RETARD",IF($B62&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I62" s="51" t="inlineStr">
@@ -43566,7 +43076,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="87">
-        <f>IF(AND($B63="",$D63=""),"",IF($F63&lt;=0,"PAYÉ",IF($B63="","SANS DATE",IF($B63&lt;TODAY(),"EN RETARD",IF($B63&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B63="",$D63=""),"",IF($F63&lt;=0,"PAYÉ",IF($B63="","SANS DATE",IF($B63&lt;TODAY(),"EN RETARD",IF($B63&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I63" s="51" t="inlineStr"/>
@@ -43597,7 +43107,7 @@
         <v>15000</v>
       </c>
       <c r="H64" s="87">
-        <f>IF(AND($B64="",$D64=""),"",IF($F64&lt;=0,"PAYÉ",IF($B64="","SANS DATE",IF($B64&lt;TODAY(),"EN RETARD",IF($B64&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B64="",$D64=""),"",IF($F64&lt;=0,"PAYÉ",IF($B64="","SANS DATE",IF($B64&lt;TODAY(),"EN RETARD",IF($B64&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I64" s="51" t="inlineStr">
@@ -43632,7 +43142,7 @@
         <v>25274</v>
       </c>
       <c r="H65" s="87">
-        <f>IF(AND($B65="",$D65=""),"",IF($F65&lt;=0,"PAYÉ",IF($B65="","SANS DATE",IF($B65&lt;TODAY(),"EN RETARD",IF($B65&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B65="",$D65=""),"",IF($F65&lt;=0,"PAYÉ",IF($B65="","SANS DATE",IF($B65&lt;TODAY(),"EN RETARD",IF($B65&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I65" s="51" t="inlineStr">
@@ -43667,7 +43177,7 @@
         <v>28000</v>
       </c>
       <c r="H66" s="87">
-        <f>IF(AND($B66="",$D66=""),"",IF($F66&lt;=0,"PAYÉ",IF($B66="","SANS DATE",IF($B66&lt;TODAY(),"EN RETARD",IF($B66&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B66="",$D66=""),"",IF($F66&lt;=0,"PAYÉ",IF($B66="","SANS DATE",IF($B66&lt;TODAY(),"EN RETARD",IF($B66&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I66" s="51" t="inlineStr">
@@ -43702,7 +43212,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="87">
-        <f>IF(AND($B67="",$D67=""),"",IF($F67&lt;=0,"PAYÉ",IF($B67="","SANS DATE",IF($B67&lt;TODAY(),"EN RETARD",IF($B67&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B67="",$D67=""),"",IF($F67&lt;=0,"PAYÉ",IF($B67="","SANS DATE",IF($B67&lt;TODAY(),"EN RETARD",IF($B67&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I67" s="51" t="inlineStr"/>
@@ -43733,7 +43243,7 @@
         <v>9300</v>
       </c>
       <c r="H68" s="87">
-        <f>IF(AND($B68="",$D68=""),"",IF($F68&lt;=0,"PAYÉ",IF($B68="","SANS DATE",IF($B68&lt;TODAY(),"EN RETARD",IF($B68&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B68="",$D68=""),"",IF($F68&lt;=0,"PAYÉ",IF($B68="","SANS DATE",IF($B68&lt;TODAY(),"EN RETARD",IF($B68&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I68" s="51" t="inlineStr">
@@ -43768,7 +43278,7 @@
         <v>28241</v>
       </c>
       <c r="H69" s="87">
-        <f>IF(AND($B69="",$D69=""),"",IF($F69&lt;=0,"PAYÉ",IF($B69="","SANS DATE",IF($B69&lt;TODAY(),"EN RETARD",IF($B69&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B69="",$D69=""),"",IF($F69&lt;=0,"PAYÉ",IF($B69="","SANS DATE",IF($B69&lt;TODAY(),"EN RETARD",IF($B69&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I69" s="51" t="inlineStr">
@@ -43799,7 +43309,7 @@
         <v>2372.62</v>
       </c>
       <c r="H70" s="87">
-        <f>IF(AND($B70="",$D70=""),"",IF($F70&lt;=0,"PAYÉ",IF($B70="","SANS DATE",IF($B70&lt;TODAY(),"EN RETARD",IF($B70&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B70="",$D70=""),"",IF($F70&lt;=0,"PAYÉ",IF($B70="","SANS DATE",IF($B70&lt;TODAY(),"EN RETARD",IF($B70&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I70" s="51" t="inlineStr">
@@ -43834,7 +43344,7 @@
         <v>14580</v>
       </c>
       <c r="H71" s="87">
-        <f>IF(AND($B71="",$D71=""),"",IF($F71&lt;=0,"PAYÉ",IF($B71="","SANS DATE",IF($B71&lt;TODAY(),"EN RETARD",IF($B71&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B71="",$D71=""),"",IF($F71&lt;=0,"PAYÉ",IF($B71="","SANS DATE",IF($B71&lt;TODAY(),"EN RETARD",IF($B71&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I71" s="51" t="inlineStr">
@@ -43869,7 +43379,7 @@
         <v>27000</v>
       </c>
       <c r="H72" s="87">
-        <f>IF(AND($B72="",$D72=""),"",IF($F72&lt;=0,"PAYÉ",IF($B72="","SANS DATE",IF($B72&lt;TODAY(),"EN RETARD",IF($B72&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B72="",$D72=""),"",IF($F72&lt;=0,"PAYÉ",IF($B72="","SANS DATE",IF($B72&lt;TODAY(),"EN RETARD",IF($B72&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I72" s="51" t="inlineStr">
@@ -43904,7 +43414,7 @@
         <v>28500</v>
       </c>
       <c r="H73" s="87">
-        <f>IF(AND($B73="",$D73=""),"",IF($F73&lt;=0,"PAYÉ",IF($B73="","SANS DATE",IF($B73&lt;TODAY(),"EN RETARD",IF($B73&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B73="",$D73=""),"",IF($F73&lt;=0,"PAYÉ",IF($B73="","SANS DATE",IF($B73&lt;TODAY(),"EN RETARD",IF($B73&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I73" s="51" t="inlineStr">
@@ -43939,7 +43449,7 @@
         <v>28500</v>
       </c>
       <c r="H74" s="87">
-        <f>IF(AND($B74="",$D74=""),"",IF($F74&lt;=0,"PAYÉ",IF($B74="","SANS DATE",IF($B74&lt;TODAY(),"EN RETARD",IF($B74&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B74="",$D74=""),"",IF($F74&lt;=0,"PAYÉ",IF($B74="","SANS DATE",IF($B74&lt;TODAY(),"EN RETARD",IF($B74&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I74" s="51" t="inlineStr">
@@ -43974,7 +43484,7 @@
         <v>20000</v>
       </c>
       <c r="H75" s="87">
-        <f>IF(AND($B75="",$D75=""),"",IF($F75&lt;=0,"PAYÉ",IF($B75="","SANS DATE",IF($B75&lt;TODAY(),"EN RETARD",IF($B75&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B75="",$D75=""),"",IF($F75&lt;=0,"PAYÉ",IF($B75="","SANS DATE",IF($B75&lt;TODAY(),"EN RETARD",IF($B75&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I75" s="51" t="inlineStr">
@@ -44009,7 +43519,7 @@
         <v>29000</v>
       </c>
       <c r="H76" s="87">
-        <f>IF(AND($B76="",$D76=""),"",IF($F76&lt;=0,"PAYÉ",IF($B76="","SANS DATE",IF($B76&lt;TODAY(),"EN RETARD",IF($B76&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B76="",$D76=""),"",IF($F76&lt;=0,"PAYÉ",IF($B76="","SANS DATE",IF($B76&lt;TODAY(),"EN RETARD",IF($B76&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I76" s="51" t="inlineStr">
@@ -44040,7 +43550,7 @@
         <v>6000</v>
       </c>
       <c r="H77" s="87">
-        <f>IF(AND($B77="",$D77=""),"",IF($F77&lt;=0,"PAYÉ",IF($B77="","SANS DATE",IF($B77&lt;TODAY(),"EN RETARD",IF($B77&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B77="",$D77=""),"",IF($F77&lt;=0,"PAYÉ",IF($B77="","SANS DATE",IF($B77&lt;TODAY(),"EN RETARD",IF($B77&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I77" s="51" t="inlineStr">
@@ -44075,7 +43585,7 @@
         <v>12500</v>
       </c>
       <c r="H78" s="87">
-        <f>IF(AND($B78="",$D78=""),"",IF($F78&lt;=0,"PAYÉ",IF($B78="","SANS DATE",IF($B78&lt;TODAY(),"EN RETARD",IF($B78&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B78="",$D78=""),"",IF($F78&lt;=0,"PAYÉ",IF($B78="","SANS DATE",IF($B78&lt;TODAY(),"EN RETARD",IF($B78&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I78" s="51" t="inlineStr">
@@ -44110,7 +43620,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="87">
-        <f>IF(AND($B79="",$D79=""),"",IF($F79&lt;=0,"PAYÉ",IF($B79="","SANS DATE",IF($B79&lt;TODAY(),"EN RETARD",IF($B79&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B79="",$D79=""),"",IF($F79&lt;=0,"PAYÉ",IF($B79="","SANS DATE",IF($B79&lt;TODAY(),"EN RETARD",IF($B79&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I79" s="51" t="inlineStr"/>
@@ -44141,7 +43651,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="87">
-        <f>IF(AND($B80="",$D80=""),"",IF($F80&lt;=0,"PAYÉ",IF($B80="","SANS DATE",IF($B80&lt;TODAY(),"EN RETARD",IF($B80&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B80="",$D80=""),"",IF($F80&lt;=0,"PAYÉ",IF($B80="","SANS DATE",IF($B80&lt;TODAY(),"EN RETARD",IF($B80&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I80" s="51" t="inlineStr"/>
@@ -44172,7 +43682,7 @@
         <v>0</v>
       </c>
       <c r="H81" s="87">
-        <f>IF(AND($B81="",$D81=""),"",IF($F81&lt;=0,"PAYÉ",IF($B81="","SANS DATE",IF($B81&lt;TODAY(),"EN RETARD",IF($B81&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B81="",$D81=""),"",IF($F81&lt;=0,"PAYÉ",IF($B81="","SANS DATE",IF($B81&lt;TODAY(),"EN RETARD",IF($B81&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I81" s="51" t="inlineStr"/>
@@ -44203,7 +43713,7 @@
         <v>0</v>
       </c>
       <c r="H82" s="87">
-        <f>IF(AND($B82="",$D82=""),"",IF($F82&lt;=0,"PAYÉ",IF($B82="","SANS DATE",IF($B82&lt;TODAY(),"EN RETARD",IF($B82&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B82="",$D82=""),"",IF($F82&lt;=0,"PAYÉ",IF($B82="","SANS DATE",IF($B82&lt;TODAY(),"EN RETARD",IF($B82&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I82" s="51" t="inlineStr"/>
@@ -44234,7 +43744,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="87">
-        <f>IF(AND($B83="",$D83=""),"",IF($F83&lt;=0,"PAYÉ",IF($B83="","SANS DATE",IF($B83&lt;TODAY(),"EN RETARD",IF($B83&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B83="",$D83=""),"",IF($F83&lt;=0,"PAYÉ",IF($B83="","SANS DATE",IF($B83&lt;TODAY(),"EN RETARD",IF($B83&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I83" s="51" t="inlineStr"/>
@@ -44265,7 +43775,7 @@
         <v>0</v>
       </c>
       <c r="H84" s="87">
-        <f>IF(AND($B84="",$D84=""),"",IF($F84&lt;=0,"PAYÉ",IF($B84="","SANS DATE",IF($B84&lt;TODAY(),"EN RETARD",IF($B84&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B84="",$D84=""),"",IF($F84&lt;=0,"PAYÉ",IF($B84="","SANS DATE",IF($B84&lt;TODAY(),"EN RETARD",IF($B84&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I84" s="51" t="inlineStr"/>
@@ -44296,7 +43806,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="87">
-        <f>IF(AND($B85="",$D85=""),"",IF($F85&lt;=0,"PAYÉ",IF($B85="","SANS DATE",IF($B85&lt;TODAY(),"EN RETARD",IF($B85&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B85="",$D85=""),"",IF($F85&lt;=0,"PAYÉ",IF($B85="","SANS DATE",IF($B85&lt;TODAY(),"EN RETARD",IF($B85&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I85" s="51" t="inlineStr"/>
@@ -44327,7 +43837,7 @@
         <v>0</v>
       </c>
       <c r="H86" s="87">
-        <f>IF(AND($B86="",$D86=""),"",IF($F86&lt;=0,"PAYÉ",IF($B86="","SANS DATE",IF($B86&lt;TODAY(),"EN RETARD",IF($B86&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B86="",$D86=""),"",IF($F86&lt;=0,"PAYÉ",IF($B86="","SANS DATE",IF($B86&lt;TODAY(),"EN RETARD",IF($B86&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I86" s="51" t="inlineStr"/>
@@ -44358,7 +43868,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="87">
-        <f>IF(AND($B87="",$D87=""),"",IF($F87&lt;=0,"PAYÉ",IF($B87="","SANS DATE",IF($B87&lt;TODAY(),"EN RETARD",IF($B87&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B87="",$D87=""),"",IF($F87&lt;=0,"PAYÉ",IF($B87="","SANS DATE",IF($B87&lt;TODAY(),"EN RETARD",IF($B87&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I87" s="51" t="inlineStr"/>
@@ -44389,7 +43899,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="87">
-        <f>IF(AND($B88="",$D88=""),"",IF($F88&lt;=0,"PAYÉ",IF($B88="","SANS DATE",IF($B88&lt;TODAY(),"EN RETARD",IF($B88&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B88="",$D88=""),"",IF($F88&lt;=0,"PAYÉ",IF($B88="","SANS DATE",IF($B88&lt;TODAY(),"EN RETARD",IF($B88&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I88" s="51" t="inlineStr"/>
@@ -44420,7 +43930,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="87">
-        <f>IF(AND($B89="",$D89=""),"",IF($F89&lt;=0,"PAYÉ",IF($B89="","SANS DATE",IF($B89&lt;TODAY(),"EN RETARD",IF($B89&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B89="",$D89=""),"",IF($F89&lt;=0,"PAYÉ",IF($B89="","SANS DATE",IF($B89&lt;TODAY(),"EN RETARD",IF($B89&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I89" s="51" t="inlineStr"/>
@@ -44451,7 +43961,7 @@
         <v>0</v>
       </c>
       <c r="H90" s="87">
-        <f>IF(AND($B90="",$D90=""),"",IF($F90&lt;=0,"PAYÉ",IF($B90="","SANS DATE",IF($B90&lt;TODAY(),"EN RETARD",IF($B90&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B90="",$D90=""),"",IF($F90&lt;=0,"PAYÉ",IF($B90="","SANS DATE",IF($B90&lt;TODAY(),"EN RETARD",IF($B90&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I90" s="51" t="inlineStr"/>
@@ -44482,7 +43992,7 @@
         <v>0</v>
       </c>
       <c r="H91" s="87">
-        <f>IF(AND($B91="",$D91=""),"",IF($F91&lt;=0,"PAYÉ",IF($B91="","SANS DATE",IF($B91&lt;TODAY(),"EN RETARD",IF($B91&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B91="",$D91=""),"",IF($F91&lt;=0,"PAYÉ",IF($B91="","SANS DATE",IF($B91&lt;TODAY(),"EN RETARD",IF($B91&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I91" s="51" t="inlineStr"/>
@@ -44513,7 +44023,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="87">
-        <f>IF(AND($B92="",$D92=""),"",IF($F92&lt;=0,"PAYÉ",IF($B92="","SANS DATE",IF($B92&lt;TODAY(),"EN RETARD",IF($B92&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B92="",$D92=""),"",IF($F92&lt;=0,"PAYÉ",IF($B92="","SANS DATE",IF($B92&lt;TODAY(),"EN RETARD",IF($B92&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I92" s="51" t="inlineStr"/>
@@ -44544,7 +44054,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="87">
-        <f>IF(AND($B93="",$D93=""),"",IF($F93&lt;=0,"PAYÉ",IF($B93="","SANS DATE",IF($B93&lt;TODAY(),"EN RETARD",IF($B93&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B93="",$D93=""),"",IF($F93&lt;=0,"PAYÉ",IF($B93="","SANS DATE",IF($B93&lt;TODAY(),"EN RETARD",IF($B93&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I93" s="51" t="inlineStr"/>
@@ -44575,7 +44085,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="87">
-        <f>IF(AND($B94="",$D94=""),"",IF($F94&lt;=0,"PAYÉ",IF($B94="","SANS DATE",IF($B94&lt;TODAY(),"EN RETARD",IF($B94&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B94="",$D94=""),"",IF($F94&lt;=0,"PAYÉ",IF($B94="","SANS DATE",IF($B94&lt;TODAY(),"EN RETARD",IF($B94&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I94" s="51" t="inlineStr"/>
@@ -44606,7 +44116,7 @@
         <v>0</v>
       </c>
       <c r="H95" s="87">
-        <f>IF(AND($B95="",$D95=""),"",IF($F95&lt;=0,"PAYÉ",IF($B95="","SANS DATE",IF($B95&lt;TODAY(),"EN RETARD",IF($B95&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B95="",$D95=""),"",IF($F95&lt;=0,"PAYÉ",IF($B95="","SANS DATE",IF($B95&lt;TODAY(),"EN RETARD",IF($B95&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I95" s="51" t="inlineStr"/>
@@ -44637,7 +44147,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="87">
-        <f>IF(AND($B96="",$D96=""),"",IF($F96&lt;=0,"PAYÉ",IF($B96="","SANS DATE",IF($B96&lt;TODAY(),"EN RETARD",IF($B96&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B96="",$D96=""),"",IF($F96&lt;=0,"PAYÉ",IF($B96="","SANS DATE",IF($B96&lt;TODAY(),"EN RETARD",IF($B96&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I96" s="51" t="inlineStr"/>
@@ -44668,7 +44178,7 @@
         <v>0</v>
       </c>
       <c r="H97" s="87">
-        <f>IF(AND($B97="",$D97=""),"",IF($F97&lt;=0,"PAYÉ",IF($B97="","SANS DATE",IF($B97&lt;TODAY(),"EN RETARD",IF($B97&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B97="",$D97=""),"",IF($F97&lt;=0,"PAYÉ",IF($B97="","SANS DATE",IF($B97&lt;TODAY(),"EN RETARD",IF($B97&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I97" s="51" t="inlineStr"/>
@@ -44699,7 +44209,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="87">
-        <f>IF(AND($B98="",$D98=""),"",IF($F98&lt;=0,"PAYÉ",IF($B98="","SANS DATE",IF($B98&lt;TODAY(),"EN RETARD",IF($B98&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B98="",$D98=""),"",IF($F98&lt;=0,"PAYÉ",IF($B98="","SANS DATE",IF($B98&lt;TODAY(),"EN RETARD",IF($B98&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I98" s="51" t="inlineStr"/>
@@ -44730,7 +44240,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="87">
-        <f>IF(AND($B99="",$D99=""),"",IF($F99&lt;=0,"PAYÉ",IF($B99="","SANS DATE",IF($B99&lt;TODAY(),"EN RETARD",IF($B99&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B99="",$D99=""),"",IF($F99&lt;=0,"PAYÉ",IF($B99="","SANS DATE",IF($B99&lt;TODAY(),"EN RETARD",IF($B99&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I99" s="51" t="inlineStr"/>
@@ -44761,7 +44271,7 @@
         <v>0</v>
       </c>
       <c r="H100" s="87">
-        <f>IF(AND($B100="",$D100=""),"",IF($F100&lt;=0,"PAYÉ",IF($B100="","SANS DATE",IF($B100&lt;TODAY(),"EN RETARD",IF($B100&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B100="",$D100=""),"",IF($F100&lt;=0,"PAYÉ",IF($B100="","SANS DATE",IF($B100&lt;TODAY(),"EN RETARD",IF($B100&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I100" s="51" t="inlineStr"/>
@@ -44792,7 +44302,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="87">
-        <f>IF(AND($B101="",$D101=""),"",IF($F101&lt;=0,"PAYÉ",IF($B101="","SANS DATE",IF($B101&lt;TODAY(),"EN RETARD",IF($B101&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B101="",$D101=""),"",IF($F101&lt;=0,"PAYÉ",IF($B101="","SANS DATE",IF($B101&lt;TODAY(),"EN RETARD",IF($B101&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I101" s="51" t="inlineStr"/>
@@ -44823,7 +44333,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="87">
-        <f>IF(AND($B102="",$D102=""),"",IF($F102&lt;=0,"PAYÉ",IF($B102="","SANS DATE",IF($B102&lt;TODAY(),"EN RETARD",IF($B102&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B102="",$D102=""),"",IF($F102&lt;=0,"PAYÉ",IF($B102="","SANS DATE",IF($B102&lt;TODAY(),"EN RETARD",IF($B102&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I102" s="51" t="inlineStr"/>
@@ -44854,7 +44364,7 @@
         <v>0</v>
       </c>
       <c r="H103" s="87">
-        <f>IF(AND($B103="",$D103=""),"",IF($F103&lt;=0,"PAYÉ",IF($B103="","SANS DATE",IF($B103&lt;TODAY(),"EN RETARD",IF($B103&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B103="",$D103=""),"",IF($F103&lt;=0,"PAYÉ",IF($B103="","SANS DATE",IF($B103&lt;TODAY(),"EN RETARD",IF($B103&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I103" s="51" t="inlineStr"/>
@@ -44879,7 +44389,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="87">
-        <f>IF(AND($B104="",$D104=""),"",IF($F104&lt;=0,"PAYÉ",IF($B104="","SANS DATE",IF($B104&lt;TODAY(),"EN RETARD",IF($B104&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B104="",$D104=""),"",IF($F104&lt;=0,"PAYÉ",IF($B104="","SANS DATE",IF($B104&lt;TODAY(),"EN RETARD",IF($B104&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I104" s="51" t="inlineStr">
@@ -44908,7 +44418,7 @@
         <v>0</v>
       </c>
       <c r="H105" s="87">
-        <f>IF(AND($B105="",$D105=""),"",IF($F105&lt;=0,"PAYÉ",IF($B105="","SANS DATE",IF($B105&lt;TODAY(),"EN RETARD",IF($B105&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B105="",$D105=""),"",IF($F105&lt;=0,"PAYÉ",IF($B105="","SANS DATE",IF($B105&lt;TODAY(),"EN RETARD",IF($B105&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I105" s="51" t="inlineStr">
@@ -44937,7 +44447,7 @@
         <v>0</v>
       </c>
       <c r="H106" s="87">
-        <f>IF(AND($B106="",$D106=""),"",IF($F106&lt;=0,"PAYÉ",IF($B106="","SANS DATE",IF($B106&lt;TODAY(),"EN RETARD",IF($B106&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B106="",$D106=""),"",IF($F106&lt;=0,"PAYÉ",IF($B106="","SANS DATE",IF($B106&lt;TODAY(),"EN RETARD",IF($B106&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I106" s="51" t="inlineStr"/>
@@ -44962,7 +44472,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="87">
-        <f>IF(AND($B107="",$D107=""),"",IF($F107&lt;=0,"PAYÉ",IF($B107="","SANS DATE",IF($B107&lt;TODAY(),"EN RETARD",IF($B107&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B107="",$D107=""),"",IF($F107&lt;=0,"PAYÉ",IF($B107="","SANS DATE",IF($B107&lt;TODAY(),"EN RETARD",IF($B107&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I107" s="51" t="inlineStr"/>
@@ -44975,7 +44485,7 @@
       <c r="F108" s="30" t="n"/>
       <c r="G108" s="30" t="n"/>
       <c r="H108" s="87">
-        <f>IF(AND($B108="",$D108=""),"",IF($F108&lt;=0,"PAYÉ",IF($B108="","SANS DATE",IF($B108&lt;TODAY(),"EN RETARD",IF($B108&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B108="",$D108=""),"",IF($F108&lt;=0,"PAYÉ",IF($B108="","SANS DATE",IF($B108&lt;TODAY(),"EN RETARD",IF($B108&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I108" s="51" t="n"/>
@@ -44988,7 +44498,7 @@
       <c r="F109" s="30" t="n"/>
       <c r="G109" s="30" t="n"/>
       <c r="H109" s="87">
-        <f>IF(AND($B109="",$D109=""),"",IF($F109&lt;=0,"PAYÉ",IF($B109="","SANS DATE",IF($B109&lt;TODAY(),"EN RETARD",IF($B109&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B109="",$D109=""),"",IF($F109&lt;=0,"PAYÉ",IF($B109="","SANS DATE",IF($B109&lt;TODAY(),"EN RETARD",IF($B109&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I109" s="51" t="n"/>
@@ -45001,7 +44511,7 @@
       <c r="F110" s="30" t="n"/>
       <c r="G110" s="30" t="n"/>
       <c r="H110" s="87">
-        <f>IF(AND($B110="",$D110=""),"",IF($F110&lt;=0,"PAYÉ",IF($B110="","SANS DATE",IF($B110&lt;TODAY(),"EN RETARD",IF($B110&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B110="",$D110=""),"",IF($F110&lt;=0,"PAYÉ",IF($B110="","SANS DATE",IF($B110&lt;TODAY(),"EN RETARD",IF($B110&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I110" s="51" t="n"/>
@@ -45014,7 +44524,7 @@
       <c r="F111" s="30" t="n"/>
       <c r="G111" s="30" t="n"/>
       <c r="H111" s="87">
-        <f>IF(AND($B111="",$D111=""),"",IF($F111&lt;=0,"PAYÉ",IF($B111="","SANS DATE",IF($B111&lt;TODAY(),"EN RETARD",IF($B111&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B111="",$D111=""),"",IF($F111&lt;=0,"PAYÉ",IF($B111="","SANS DATE",IF($B111&lt;TODAY(),"EN RETARD",IF($B111&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I111" s="51" t="n"/>
@@ -45027,7 +44537,7 @@
       <c r="F112" s="30" t="n"/>
       <c r="G112" s="30" t="n"/>
       <c r="H112" s="87">
-        <f>IF(AND($B112="",$D112=""),"",IF($F112&lt;=0,"PAYÉ",IF($B112="","SANS DATE",IF($B112&lt;TODAY(),"EN RETARD",IF($B112&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B112="",$D112=""),"",IF($F112&lt;=0,"PAYÉ",IF($B112="","SANS DATE",IF($B112&lt;TODAY(),"EN RETARD",IF($B112&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I112" s="51" t="n"/>
@@ -45040,7 +44550,7 @@
       <c r="F113" s="30" t="n"/>
       <c r="G113" s="30" t="n"/>
       <c r="H113" s="87">
-        <f>IF(AND($B113="",$D113=""),"",IF($F113&lt;=0,"PAYÉ",IF($B113="","SANS DATE",IF($B113&lt;TODAY(),"EN RETARD",IF($B113&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B113="",$D113=""),"",IF($F113&lt;=0,"PAYÉ",IF($B113="","SANS DATE",IF($B113&lt;TODAY(),"EN RETARD",IF($B113&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I113" s="51" t="n"/>
@@ -45053,7 +44563,7 @@
       <c r="F114" s="30" t="n"/>
       <c r="G114" s="30" t="n"/>
       <c r="H114" s="87">
-        <f>IF(AND($B114="",$D114=""),"",IF($F114&lt;=0,"PAYÉ",IF($B114="","SANS DATE",IF($B114&lt;TODAY(),"EN RETARD",IF($B114&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B114="",$D114=""),"",IF($F114&lt;=0,"PAYÉ",IF($B114="","SANS DATE",IF($B114&lt;TODAY(),"EN RETARD",IF($B114&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I114" s="51" t="n"/>
@@ -45066,7 +44576,7 @@
       <c r="F115" s="30" t="n"/>
       <c r="G115" s="30" t="n"/>
       <c r="H115" s="87">
-        <f>IF(AND($B115="",$D115=""),"",IF($F115&lt;=0,"PAYÉ",IF($B115="","SANS DATE",IF($B115&lt;TODAY(),"EN RETARD",IF($B115&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B115="",$D115=""),"",IF($F115&lt;=0,"PAYÉ",IF($B115="","SANS DATE",IF($B115&lt;TODAY(),"EN RETARD",IF($B115&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I115" s="51" t="n"/>
@@ -45079,7 +44589,7 @@
       <c r="F116" s="30" t="n"/>
       <c r="G116" s="30" t="n"/>
       <c r="H116" s="87">
-        <f>IF(AND($B116="",$D116=""),"",IF($F116&lt;=0,"PAYÉ",IF($B116="","SANS DATE",IF($B116&lt;TODAY(),"EN RETARD",IF($B116&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B116="",$D116=""),"",IF($F116&lt;=0,"PAYÉ",IF($B116="","SANS DATE",IF($B116&lt;TODAY(),"EN RETARD",IF($B116&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I116" s="51" t="n"/>
@@ -45092,7 +44602,7 @@
       <c r="F117" s="30" t="n"/>
       <c r="G117" s="30" t="n"/>
       <c r="H117" s="87">
-        <f>IF(AND($B117="",$D117=""),"",IF($F117&lt;=0,"PAYÉ",IF($B117="","SANS DATE",IF($B117&lt;TODAY(),"EN RETARD",IF($B117&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B117="",$D117=""),"",IF($F117&lt;=0,"PAYÉ",IF($B117="","SANS DATE",IF($B117&lt;TODAY(),"EN RETARD",IF($B117&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I117" s="51" t="n"/>
@@ -45105,7 +44615,7 @@
       <c r="F118" s="30" t="n"/>
       <c r="G118" s="30" t="n"/>
       <c r="H118" s="87">
-        <f>IF(AND($B118="",$D118=""),"",IF($F118&lt;=0,"PAYÉ",IF($B118="","SANS DATE",IF($B118&lt;TODAY(),"EN RETARD",IF($B118&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B118="",$D118=""),"",IF($F118&lt;=0,"PAYÉ",IF($B118="","SANS DATE",IF($B118&lt;TODAY(),"EN RETARD",IF($B118&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I118" s="51" t="n"/>
@@ -45118,7 +44628,7 @@
       <c r="F119" s="30" t="n"/>
       <c r="G119" s="30" t="n"/>
       <c r="H119" s="87">
-        <f>IF(AND($B119="",$D119=""),"",IF($F119&lt;=0,"PAYÉ",IF($B119="","SANS DATE",IF($B119&lt;TODAY(),"EN RETARD",IF($B119&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B119="",$D119=""),"",IF($F119&lt;=0,"PAYÉ",IF($B119="","SANS DATE",IF($B119&lt;TODAY(),"EN RETARD",IF($B119&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I119" s="51" t="n"/>
@@ -45131,7 +44641,7 @@
       <c r="F120" s="30" t="n"/>
       <c r="G120" s="30" t="n"/>
       <c r="H120" s="87">
-        <f>IF(AND($B120="",$D120=""),"",IF($F120&lt;=0,"PAYÉ",IF($B120="","SANS DATE",IF($B120&lt;TODAY(),"EN RETARD",IF($B120&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B120="",$D120=""),"",IF($F120&lt;=0,"PAYÉ",IF($B120="","SANS DATE",IF($B120&lt;TODAY(),"EN RETARD",IF($B120&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I120" s="51" t="n"/>
@@ -45144,7 +44654,7 @@
       <c r="F121" s="30" t="n"/>
       <c r="G121" s="30" t="n"/>
       <c r="H121" s="87">
-        <f>IF(AND($B121="",$D121=""),"",IF($F121&lt;=0,"PAYÉ",IF($B121="","SANS DATE",IF($B121&lt;TODAY(),"EN RETARD",IF($B121&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B121="",$D121=""),"",IF($F121&lt;=0,"PAYÉ",IF($B121="","SANS DATE",IF($B121&lt;TODAY(),"EN RETARD",IF($B121&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I121" s="51" t="n"/>
@@ -45157,7 +44667,7 @@
       <c r="F122" s="30" t="n"/>
       <c r="G122" s="30" t="n"/>
       <c r="H122" s="87">
-        <f>IF(AND($B122="",$D122=""),"",IF($F122&lt;=0,"PAYÉ",IF($B122="","SANS DATE",IF($B122&lt;TODAY(),"EN RETARD",IF($B122&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B122="",$D122=""),"",IF($F122&lt;=0,"PAYÉ",IF($B122="","SANS DATE",IF($B122&lt;TODAY(),"EN RETARD",IF($B122&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I122" s="51" t="n"/>
@@ -45170,7 +44680,7 @@
       <c r="F123" s="30" t="n"/>
       <c r="G123" s="30" t="n"/>
       <c r="H123" s="87">
-        <f>IF(AND($B123="",$D123=""),"",IF($F123&lt;=0,"PAYÉ",IF($B123="","SANS DATE",IF($B123&lt;TODAY(),"EN RETARD",IF($B123&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B123="",$D123=""),"",IF($F123&lt;=0,"PAYÉ",IF($B123="","SANS DATE",IF($B123&lt;TODAY(),"EN RETARD",IF($B123&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I123" s="51" t="n"/>
@@ -45183,7 +44693,7 @@
       <c r="F124" s="30" t="n"/>
       <c r="G124" s="30" t="n"/>
       <c r="H124" s="87">
-        <f>IF(AND($B124="",$D124=""),"",IF($F124&lt;=0,"PAYÉ",IF($B124="","SANS DATE",IF($B124&lt;TODAY(),"EN RETARD",IF($B124&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B124="",$D124=""),"",IF($F124&lt;=0,"PAYÉ",IF($B124="","SANS DATE",IF($B124&lt;TODAY(),"EN RETARD",IF($B124&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I124" s="51" t="n"/>
@@ -45196,7 +44706,7 @@
       <c r="F125" s="30" t="n"/>
       <c r="G125" s="30" t="n"/>
       <c r="H125" s="87">
-        <f>IF(AND($B125="",$D125=""),"",IF($F125&lt;=0,"PAYÉ",IF($B125="","SANS DATE",IF($B125&lt;TODAY(),"EN RETARD",IF($B125&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B125="",$D125=""),"",IF($F125&lt;=0,"PAYÉ",IF($B125="","SANS DATE",IF($B125&lt;TODAY(),"EN RETARD",IF($B125&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I125" s="51" t="n"/>
@@ -45209,7 +44719,7 @@
       <c r="F126" s="30" t="n"/>
       <c r="G126" s="30" t="n"/>
       <c r="H126" s="87">
-        <f>IF(AND($B126="",$D126=""),"",IF($F126&lt;=0,"PAYÉ",IF($B126="","SANS DATE",IF($B126&lt;TODAY(),"EN RETARD",IF($B126&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B126="",$D126=""),"",IF($F126&lt;=0,"PAYÉ",IF($B126="","SANS DATE",IF($B126&lt;TODAY(),"EN RETARD",IF($B126&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I126" s="51" t="n"/>
@@ -45222,7 +44732,7 @@
       <c r="F127" s="30" t="n"/>
       <c r="G127" s="30" t="n"/>
       <c r="H127" s="87">
-        <f>IF(AND($B127="",$D127=""),"",IF($F127&lt;=0,"PAYÉ",IF($B127="","SANS DATE",IF($B127&lt;TODAY(),"EN RETARD",IF($B127&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B127="",$D127=""),"",IF($F127&lt;=0,"PAYÉ",IF($B127="","SANS DATE",IF($B127&lt;TODAY(),"EN RETARD",IF($B127&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I127" s="51" t="n"/>
@@ -45235,7 +44745,7 @@
       <c r="F128" s="30" t="n"/>
       <c r="G128" s="30" t="n"/>
       <c r="H128" s="87">
-        <f>IF(AND($B128="",$D128=""),"",IF($F128&lt;=0,"PAYÉ",IF($B128="","SANS DATE",IF($B128&lt;TODAY(),"EN RETARD",IF($B128&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B128="",$D128=""),"",IF($F128&lt;=0,"PAYÉ",IF($B128="","SANS DATE",IF($B128&lt;TODAY(),"EN RETARD",IF($B128&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I128" s="51" t="n"/>
@@ -45248,7 +44758,7 @@
       <c r="F129" s="30" t="n"/>
       <c r="G129" s="30" t="n"/>
       <c r="H129" s="87">
-        <f>IF(AND($B129="",$D129=""),"",IF($F129&lt;=0,"PAYÉ",IF($B129="","SANS DATE",IF($B129&lt;TODAY(),"EN RETARD",IF($B129&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B129="",$D129=""),"",IF($F129&lt;=0,"PAYÉ",IF($B129="","SANS DATE",IF($B129&lt;TODAY(),"EN RETARD",IF($B129&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I129" s="51" t="n"/>
@@ -45261,7 +44771,7 @@
       <c r="F130" s="30" t="n"/>
       <c r="G130" s="30" t="n"/>
       <c r="H130" s="87">
-        <f>IF(AND($B130="",$D130=""),"",IF($F130&lt;=0,"PAYÉ",IF($B130="","SANS DATE",IF($B130&lt;TODAY(),"EN RETARD",IF($B130&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B130="",$D130=""),"",IF($F130&lt;=0,"PAYÉ",IF($B130="","SANS DATE",IF($B130&lt;TODAY(),"EN RETARD",IF($B130&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I130" s="51" t="n"/>
@@ -45274,7 +44784,7 @@
       <c r="F131" s="30" t="n"/>
       <c r="G131" s="30" t="n"/>
       <c r="H131" s="87">
-        <f>IF(AND($B131="",$D131=""),"",IF($F131&lt;=0,"PAYÉ",IF($B131="","SANS DATE",IF($B131&lt;TODAY(),"EN RETARD",IF($B131&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B131="",$D131=""),"",IF($F131&lt;=0,"PAYÉ",IF($B131="","SANS DATE",IF($B131&lt;TODAY(),"EN RETARD",IF($B131&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I131" s="51" t="n"/>
@@ -45287,7 +44797,7 @@
       <c r="F132" s="30" t="n"/>
       <c r="G132" s="30" t="n"/>
       <c r="H132" s="87">
-        <f>IF(AND($B132="",$D132=""),"",IF($F132&lt;=0,"PAYÉ",IF($B132="","SANS DATE",IF($B132&lt;TODAY(),"EN RETARD",IF($B132&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B132="",$D132=""),"",IF($F132&lt;=0,"PAYÉ",IF($B132="","SANS DATE",IF($B132&lt;TODAY(),"EN RETARD",IF($B132&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I132" s="51" t="n"/>
@@ -45300,7 +44810,7 @@
       <c r="F133" s="30" t="n"/>
       <c r="G133" s="30" t="n"/>
       <c r="H133" s="87">
-        <f>IF(AND($B133="",$D133=""),"",IF($F133&lt;=0,"PAYÉ",IF($B133="","SANS DATE",IF($B133&lt;TODAY(),"EN RETARD",IF($B133&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B133="",$D133=""),"",IF($F133&lt;=0,"PAYÉ",IF($B133="","SANS DATE",IF($B133&lt;TODAY(),"EN RETARD",IF($B133&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I133" s="51" t="n"/>
@@ -45313,7 +44823,7 @@
       <c r="F134" s="30" t="n"/>
       <c r="G134" s="30" t="n"/>
       <c r="H134" s="87">
-        <f>IF(AND($B134="",$D134=""),"",IF($F134&lt;=0,"PAYÉ",IF($B134="","SANS DATE",IF($B134&lt;TODAY(),"EN RETARD",IF($B134&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B134="",$D134=""),"",IF($F134&lt;=0,"PAYÉ",IF($B134="","SANS DATE",IF($B134&lt;TODAY(),"EN RETARD",IF($B134&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I134" s="51" t="n"/>
@@ -45326,7 +44836,7 @@
       <c r="F135" s="30" t="n"/>
       <c r="G135" s="30" t="n"/>
       <c r="H135" s="87">
-        <f>IF(AND($B135="",$D135=""),"",IF($F135&lt;=0,"PAYÉ",IF($B135="","SANS DATE",IF($B135&lt;TODAY(),"EN RETARD",IF($B135&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B135="",$D135=""),"",IF($F135&lt;=0,"PAYÉ",IF($B135="","SANS DATE",IF($B135&lt;TODAY(),"EN RETARD",IF($B135&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I135" s="51" t="n"/>
@@ -45339,7 +44849,7 @@
       <c r="F136" s="30" t="n"/>
       <c r="G136" s="30" t="n"/>
       <c r="H136" s="87">
-        <f>IF(AND($B136="",$D136=""),"",IF($F136&lt;=0,"PAYÉ",IF($B136="","SANS DATE",IF($B136&lt;TODAY(),"EN RETARD",IF($B136&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B136="",$D136=""),"",IF($F136&lt;=0,"PAYÉ",IF($B136="","SANS DATE",IF($B136&lt;TODAY(),"EN RETARD",IF($B136&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I136" s="51" t="n"/>
@@ -45352,7 +44862,7 @@
       <c r="F137" s="30" t="n"/>
       <c r="G137" s="30" t="n"/>
       <c r="H137" s="87">
-        <f>IF(AND($B137="",$D137=""),"",IF($F137&lt;=0,"PAYÉ",IF($B137="","SANS DATE",IF($B137&lt;TODAY(),"EN RETARD",IF($B137&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B137="",$D137=""),"",IF($F137&lt;=0,"PAYÉ",IF($B137="","SANS DATE",IF($B137&lt;TODAY(),"EN RETARD",IF($B137&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I137" s="51" t="n"/>
@@ -45365,7 +44875,7 @@
       <c r="F138" s="30" t="n"/>
       <c r="G138" s="30" t="n"/>
       <c r="H138" s="87">
-        <f>IF(AND($B138="",$D138=""),"",IF($F138&lt;=0,"PAYÉ",IF($B138="","SANS DATE",IF($B138&lt;TODAY(),"EN RETARD",IF($B138&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B138="",$D138=""),"",IF($F138&lt;=0,"PAYÉ",IF($B138="","SANS DATE",IF($B138&lt;TODAY(),"EN RETARD",IF($B138&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I138" s="51" t="n"/>
@@ -45378,7 +44888,7 @@
       <c r="F139" s="30" t="n"/>
       <c r="G139" s="30" t="n"/>
       <c r="H139" s="87">
-        <f>IF(AND($B139="",$D139=""),"",IF($F139&lt;=0,"PAYÉ",IF($B139="","SANS DATE",IF($B139&lt;TODAY(),"EN RETARD",IF($B139&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B139="",$D139=""),"",IF($F139&lt;=0,"PAYÉ",IF($B139="","SANS DATE",IF($B139&lt;TODAY(),"EN RETARD",IF($B139&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I139" s="51" t="n"/>
@@ -45391,7 +44901,7 @@
       <c r="F140" s="30" t="n"/>
       <c r="G140" s="30" t="n"/>
       <c r="H140" s="87">
-        <f>IF(AND($B140="",$D140=""),"",IF($F140&lt;=0,"PAYÉ",IF($B140="","SANS DATE",IF($B140&lt;TODAY(),"EN RETARD",IF($B140&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B140="",$D140=""),"",IF($F140&lt;=0,"PAYÉ",IF($B140="","SANS DATE",IF($B140&lt;TODAY(),"EN RETARD",IF($B140&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I140" s="51" t="n"/>
@@ -45404,7 +44914,7 @@
       <c r="F141" s="30" t="n"/>
       <c r="G141" s="30" t="n"/>
       <c r="H141" s="87">
-        <f>IF(AND($B141="",$D141=""),"",IF($F141&lt;=0,"PAYÉ",IF($B141="","SANS DATE",IF($B141&lt;TODAY(),"EN RETARD",IF($B141&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B141="",$D141=""),"",IF($F141&lt;=0,"PAYÉ",IF($B141="","SANS DATE",IF($B141&lt;TODAY(),"EN RETARD",IF($B141&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I141" s="51" t="n"/>
@@ -45417,7 +44927,7 @@
       <c r="F142" s="30" t="n"/>
       <c r="G142" s="30" t="n"/>
       <c r="H142" s="87">
-        <f>IF(AND($B142="",$D142=""),"",IF($F142&lt;=0,"PAYÉ",IF($B142="","SANS DATE",IF($B142&lt;TODAY(),"EN RETARD",IF($B142&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B142="",$D142=""),"",IF($F142&lt;=0,"PAYÉ",IF($B142="","SANS DATE",IF($B142&lt;TODAY(),"EN RETARD",IF($B142&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I142" s="51" t="n"/>
@@ -45430,7 +44940,7 @@
       <c r="F143" s="30" t="n"/>
       <c r="G143" s="30" t="n"/>
       <c r="H143" s="87">
-        <f>IF(AND($B143="",$D143=""),"",IF($F143&lt;=0,"PAYÉ",IF($B143="","SANS DATE",IF($B143&lt;TODAY(),"EN RETARD",IF($B143&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B143="",$D143=""),"",IF($F143&lt;=0,"PAYÉ",IF($B143="","SANS DATE",IF($B143&lt;TODAY(),"EN RETARD",IF($B143&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I143" s="51" t="n"/>
@@ -45443,7 +44953,7 @@
       <c r="F144" s="30" t="n"/>
       <c r="G144" s="30" t="n"/>
       <c r="H144" s="87">
-        <f>IF(AND($B144="",$D144=""),"",IF($F144&lt;=0,"PAYÉ",IF($B144="","SANS DATE",IF($B144&lt;TODAY(),"EN RETARD",IF($B144&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B144="",$D144=""),"",IF($F144&lt;=0,"PAYÉ",IF($B144="","SANS DATE",IF($B144&lt;TODAY(),"EN RETARD",IF($B144&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I144" s="51" t="n"/>
@@ -45456,7 +44966,7 @@
       <c r="F145" s="30" t="n"/>
       <c r="G145" s="30" t="n"/>
       <c r="H145" s="87">
-        <f>IF(AND($B145="",$D145=""),"",IF($F145&lt;=0,"PAYÉ",IF($B145="","SANS DATE",IF($B145&lt;TODAY(),"EN RETARD",IF($B145&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B145="",$D145=""),"",IF($F145&lt;=0,"PAYÉ",IF($B145="","SANS DATE",IF($B145&lt;TODAY(),"EN RETARD",IF($B145&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I145" s="51" t="n"/>
@@ -45469,7 +44979,7 @@
       <c r="F146" s="30" t="n"/>
       <c r="G146" s="30" t="n"/>
       <c r="H146" s="87">
-        <f>IF(AND($B146="",$D146=""),"",IF($F146&lt;=0,"PAYÉ",IF($B146="","SANS DATE",IF($B146&lt;TODAY(),"EN RETARD",IF($B146&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B146="",$D146=""),"",IF($F146&lt;=0,"PAYÉ",IF($B146="","SANS DATE",IF($B146&lt;TODAY(),"EN RETARD",IF($B146&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I146" s="51" t="n"/>
@@ -45482,7 +44992,7 @@
       <c r="F147" s="30" t="n"/>
       <c r="G147" s="30" t="n"/>
       <c r="H147" s="87">
-        <f>IF(AND($B147="",$D147=""),"",IF($F147&lt;=0,"PAYÉ",IF($B147="","SANS DATE",IF($B147&lt;TODAY(),"EN RETARD",IF($B147&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B147="",$D147=""),"",IF($F147&lt;=0,"PAYÉ",IF($B147="","SANS DATE",IF($B147&lt;TODAY(),"EN RETARD",IF($B147&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I147" s="51" t="n"/>
@@ -45495,7 +45005,7 @@
       <c r="F148" s="30" t="n"/>
       <c r="G148" s="30" t="n"/>
       <c r="H148" s="87">
-        <f>IF(AND($B148="",$D148=""),"",IF($F148&lt;=0,"PAYÉ",IF($B148="","SANS DATE",IF($B148&lt;TODAY(),"EN RETARD",IF($B148&lt;=TODAY()+30,"À ÉCHOIR ≤ 30 J","À VENIR")))))</f>
+        <f>IF(AND($B148="",$D148=""),"",IF($F148&lt;=0,"PAYÉ",IF($B148="","SANS DATE",IF($B148&lt;TODAY(),"EN RETARD",IF($B148&lt;=TODAY()+30,"À ÉCHOIR SOUS 30 J","À VENIR")))))</f>
         <v/>
       </c>
       <c r="I148" s="51" t="n"/>
@@ -45528,7 +45038,7 @@
       <formula>$H9="EN RETARD"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="8" stopIfTrue="0">
-      <formula>$H9="À ÉCHOIR ≤ 30 J"</formula>
+      <formula>$H9="À ÉCHOIR SOUS 30 J"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="9" stopIfTrue="0">
       <formula>$H9="PAYÉ"</formula>
@@ -48483,7 +47993,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -49887,7 +49396,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -51291,7 +50799,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -52695,7 +52202,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -54099,7 +53605,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -55503,6 +55008,5 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>